--- a/reports/빅딜/history/2026-09-27/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/history/2026-09-27/빅딜_training_mgf_report.xlsx
@@ -84,7 +84,7 @@
     <t>Scania 13</t>
   </si>
   <si>
-    <t>857</t>
+    <t>859</t>
   </si>
   <si>
     <t>34위</t>
@@ -117,7 +117,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>850</t>
+    <t>851</t>
   </si>
   <si>
     <t>38위</t>
@@ -147,7 +147,7 @@
     <t>Scania 23</t>
   </si>
   <si>
-    <t>922</t>
+    <t>924</t>
   </si>
   <si>
     <t>12위</t>
@@ -201,7 +201,7 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>918</t>
+    <t>919</t>
   </si>
   <si>
     <t>37위</t>
@@ -2046,7 +2046,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%90%EC%A3%BC%EB%A7%8C%EB%91%90</t>
   </si>
   <si>
-    <t>6경 6938조 7858억 839만</t>
+    <t>6경 7863조 6241억 5421만</t>
   </si>
   <si>
     <t>할바이</t>
@@ -2067,7 +2067,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B9%EB%B0%8D</t>
   </si>
   <si>
-    <t>222조 5745억 8968만</t>
+    <t>225조 7858억 6277만</t>
   </si>
   <si>
     <t>대구남성</t>
@@ -2103,6 +2103,15 @@
     <t>40조 2826억 5542만</t>
   </si>
   <si>
+    <t>오스띤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
+  </si>
+  <si>
+    <t>39조 7598억 3127만</t>
+  </si>
+  <si>
     <t>토벤숍이</t>
   </si>
   <si>
@@ -2112,15 +2121,6 @@
     <t>37조 9497억 6922만</t>
   </si>
   <si>
-    <t>오스띤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
-  </si>
-  <si>
-    <t>35조 12억 8580만</t>
-  </si>
-  <si>
     <t>빵신궁</t>
   </si>
   <si>
@@ -2139,7 +2139,16 @@
     <t>103</t>
   </si>
   <si>
-    <t>29조 4514억 132만</t>
+    <t>30조 3004억 723만</t>
+  </si>
+  <si>
+    <t>밀초크코</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EC%B4%88%ED%81%AC%EC%BD%94</t>
+  </si>
+  <si>
+    <t>30조 642억 2549만</t>
   </si>
   <si>
     <t>마키맛키마</t>
@@ -2154,15 +2163,6 @@
     <t>28조 4370억 1152만</t>
   </si>
   <si>
-    <t>밀초크코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EC%B4%88%ED%81%AC%EC%BD%94</t>
-  </si>
-  <si>
-    <t>28조 1153억 4015만</t>
-  </si>
-  <si>
     <t>킬혁</t>
   </si>
   <si>
@@ -2178,7 +2178,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%ED%86%B5%EB%B0%9B%EB%8A%94%EA%B0%88%EB%B9%84</t>
   </si>
   <si>
-    <t>25조 4971억 9716만</t>
+    <t>25조 5115억 6680만</t>
   </si>
   <si>
     <t>문보겨엉</t>
@@ -2226,7 +2226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
   </si>
   <si>
-    <t>20조 7626억 7590만</t>
+    <t>21조 1749억 5773만</t>
   </si>
   <si>
     <t>페프릭2</t>
@@ -2250,7 +2250,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%82%A4%EB%B9%84%ED%82%A4</t>
   </si>
   <si>
-    <t>7조 6325억 4371만</t>
+    <t>8조 2642억 6569만</t>
   </si>
   <si>
     <t>즈나니</t>
@@ -2262,7 +2262,7 @@
     <t>100</t>
   </si>
   <si>
-    <t>3조 3723억 2727만</t>
+    <t>3조 6189억 1745만</t>
   </si>
   <si>
     <t>닝윤</t>
@@ -9207,7 +9207,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9455,7 +9455,7 @@
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>203</v>
+        <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>685</v>
@@ -9487,7 +9487,7 @@
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>103</v>
+        <v>203</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>685</v>
@@ -9583,13 +9583,13 @@
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>168</v>
+        <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>706</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>43</v>
@@ -9603,22 +9603,22 @@
         <v>142</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>708</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>685</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>709</v>
